--- a/stakeholder_analysis/RACI matrix.xlsx
+++ b/stakeholder_analysis/RACI matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibh\Downloads\DLOS\stakeholder_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467E9046-50B4-48CC-B2A1-32BD969FDBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD126C91-34F1-4875-AF82-2B9A708EA430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B198B05-C545-4A12-B124-6861DD051446}"/>
   </bookViews>
@@ -225,12 +225,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -239,17 +254,17 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0C59AF-FE94-443A-8C8B-A1C1DC16DB23}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -593,306 +608,362 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" ht="5.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" ht="5.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:C21"/>
+    <mergeCell ref="A10:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
